--- a/动态属性部分样例.xlsx
+++ b/动态属性部分样例.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="12320" activeTab="1"/>
+    <workbookView windowWidth="28260" windowHeight="12560" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="产品配置参数" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">产品配置参数!$A$1:$N$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">产品配置参数!$A$1:$N$55</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="325">
   <si>
     <t>AttributeRule</t>
   </si>
@@ -2276,6 +2276,9 @@
     <t>附加商品</t>
   </si>
   <si>
+    <t>是否配置完成</t>
+  </si>
+  <si>
     <t>https://www.etsy.com/listing/4360752125/</t>
   </si>
   <si>
@@ -2316,6 +2319,9 @@
   </si>
   <si>
     <t>鸭嘴领带夹大号、Oval Box 、BOX、Square Box</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
   <si>
     <t>https://www.etsy.com/listing/4433085919/</t>
@@ -3019,6 +3025,279 @@
   </si>
   <si>
     <t>Urn for ashes, Custom Engraved Pet or Human Keepsake, Cremation Urn, Memorial Gift</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/1901353137/</t>
+  </si>
+  <si>
+    <t>硅胶绑带</t>
+  </si>
+  <si>
+    <t>狗牌配件</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silicone Rubber Holder </t>
+  </si>
+  <si>
+    <t>Silent Silicone Dog Tag Holder: Slide-On Collar Attachment</t>
+  </si>
+  <si>
+    <t>Silicone Rubber Size</t>
+  </si>
+  <si>
+    <t>Silicone only_S、Silicone only_M、Silicone only_L、Silicone only_XL</t>
+  </si>
+  <si>
+    <t>硅胶绑带的尺寸，四个尺寸</t>
+  </si>
+  <si>
+    <t>Silicone Rubber Color</t>
+  </si>
+  <si>
+    <t>Red
+Yellow
+Blue
+White
+Black
+Light Pink
+Hot Pink</t>
+  </si>
+  <si>
+    <t>这个是硅胶绑带的颜色，每个狗牌默认附加2个硅胶绑带，这里选择的是硅胶绑带的颜色</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4305925788/</t>
+  </si>
+  <si>
+    <t>开口长方形静音狗牌</t>
+  </si>
+  <si>
+    <t>静音狗牌</t>
+  </si>
+  <si>
+    <t>Open Rectangle Silent Dog Tag</t>
+  </si>
+  <si>
+    <t>Silent Slide-On Dog Tag: Personalized Stainless Steel Pet ID</t>
+  </si>
+  <si>
+    <t>Color &amp; Size</t>
+  </si>
+  <si>
+    <t>Silver_S 、Silver_M、Silver_L、Silver_XL、Gold_S、Gold_M、Gold_L、Gold_XL、Black_S、Black_M、Black_L、Blackr_XL、Rose Gold_S、Rose Gold_M、Rose Goldr_L、Rose Gold_XL、Blue_S、Blue_M、Blue_L、Blue_XL</t>
+  </si>
+  <si>
+    <t>颜色 尺寸，狗牌有5个颜色，每个颜色四个尺寸</t>
+  </si>
+  <si>
+    <t>Font</t>
+  </si>
+  <si>
+    <t>Font 1~Font 25</t>
+  </si>
+  <si>
+    <t>字体，这个输出到Excel表格的字体列</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4359765701/</t>
+  </si>
+  <si>
+    <t>Sliver、Gold、Black、Rose Gold、Blue</t>
+  </si>
+  <si>
+    <t>5个颜色</t>
+  </si>
+  <si>
+    <t>Size Options</t>
+  </si>
+  <si>
+    <t>Small
+Medium
+Large
+X-Large</t>
+  </si>
+  <si>
+    <t>四个尺寸，Small 映射csv里的S,Medium映射csv里的 M，Large映射L，X-Large映射XL</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4348238573/</t>
+  </si>
+  <si>
+    <t>尼龙哑光静音狗牌</t>
+  </si>
+  <si>
+    <t>Matte Nylon Silent Dog Tag</t>
+  </si>
+  <si>
+    <t>Personalized Slide-On Dog Tag: Silent Stainless Steel Pet ID-Nylon Elastic Band</t>
+  </si>
+  <si>
+    <t>Color &amp; Color Options</t>
+  </si>
+  <si>
+    <t>Silver_S/M、Silver_L、Silver_XL、Gold_S/M、Gold_L、Gold_XL、Black_/M、Black_L、Blackr_XL、Rose Gold_S/M、Rose Goldr_L、Rose Gold_XL</t>
+  </si>
+  <si>
+    <t>颜色 尺寸，狗牌有4个颜色，每个颜色三个尺寸S/M映射csv里的S, M</t>
+  </si>
+  <si>
+    <t>Font Option</t>
+  </si>
+  <si>
+    <t>Font #1~Font #25</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4364446574/</t>
+  </si>
+  <si>
+    <t>Personalized Silent Slide-On Dog Tag: Floral Stainless Steel Pet ID</t>
+  </si>
+  <si>
+    <t>Color Finish Options</t>
+  </si>
+  <si>
+    <t>Small/Medium
+Large
+X-Large</t>
+  </si>
+  <si>
+    <t>三个尺寸，Small/Medium 映射csv里的S, M，Large映射L，X-Large映射XL</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4359486042/</t>
+  </si>
+  <si>
+    <t>Silent Slide-On Dog Tag: Stainless Steel Pet ID with Nylon Elastic Band</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4364459472/</t>
+  </si>
+  <si>
+    <t>Personalized Floral Dog Tag: Silent Stainless Steel Pet ID with Elastic Band</t>
+  </si>
+  <si>
+    <t>Color &amp; Size Options</t>
+  </si>
+  <si>
+    <t>Silver_S/M、Silver_L、Silver_XL、Gold_S/M、Gold_L、Gold_XL、Black_/M、Black_L、Black_XL、Rose Gold_S/M、Rose Goldr_L、Rose Gold_XL</t>
+  </si>
+  <si>
+    <t>Design #1~Design #36</t>
+  </si>
+  <si>
+    <t>这个是设计风格，Design #1映射Style 1 输出到Excel的设计风格列</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/1885600332/</t>
+  </si>
+  <si>
+    <t>硅胶哑光静音狗牌</t>
+  </si>
+  <si>
+    <t>Matte Silicone Silent Dog Tag</t>
+  </si>
+  <si>
+    <t>Dog Tags-Custom Silicone Silent ID Tag For Cat Collar-Dog ID Tag Gift, Dog Collar Tag-Slide on Dog Tag-Silicone Dog ID Tag-Silent Dog Tag</t>
+  </si>
+  <si>
+    <t>Silver_S 、Silver_M、Silver_L、Silver_XL、Gold_S、Gold_M、Gold_L、Gold_XL、Black_S、Black_M、Black_L、Blackr_XL、Rose Gold_S、Rose Gold_M、Rose Goldr_L、Rose Gold_XL</t>
+  </si>
+  <si>
+    <t>颜色 尺寸，狗牌有4个颜色，每个颜色四个尺寸</t>
+  </si>
+  <si>
+    <t>Silicone Rubber Holder Color</t>
+  </si>
+  <si>
+    <t>两个硅胶绑带，颜色在Silicone Rubber Holder Color动态属性里选择</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4304958954/</t>
+  </si>
+  <si>
+    <t>Personalized Silent Silicone Dog Tag: Slide-On Collar ID, Custom Engraved, polished stainless steel</t>
+  </si>
+  <si>
+    <t>Polished  Silver_S 、Polished  Silver_M、Polished  Silver_L、Polished  Silver_XL、Polished  Gold_S、Polished  Gold_M、Polished  Gold_L、Polished  Gold_XL、Polished  Black_S、Polished  Black_M、Polished  Black_L、Polished  Blackr_XL、Polished  Rose Gold_S、Polished  Rose Gold_M、Polished  Rose Goldr_L、Polished  Rose Gold_XL</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/1883818048/</t>
+  </si>
+  <si>
+    <t>Silent Dog Tag: Personalized Silicone Slide-On Collar ID</t>
+  </si>
+  <si>
+    <t>Black_Small、Black_Medium、Black_Large、Black_X-Large</t>
+  </si>
+  <si>
+    <t>颜色 尺寸，狗牌有1个颜色，每个颜色四个尺寸</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4414762018/</t>
+  </si>
+  <si>
+    <t>硅胶亮光静音狗牌</t>
+  </si>
+  <si>
+    <t>Glossy Silicone Silent Dog Tag</t>
+  </si>
+  <si>
+    <t>Silent Personalized Dog Tag:No Jingle Silicone Cover,Custom Engraved, polished stainless</t>
+  </si>
+  <si>
+    <t>Color Options</t>
+  </si>
+  <si>
+    <t>Polished Sliver、Polished Gold、Polished Black、Polished RoseGold</t>
+  </si>
+  <si>
+    <t>4个颜色，只有颜色</t>
+  </si>
+  <si>
+    <t>S
+M
+L
+XL</t>
+  </si>
+  <si>
+    <t>四个尺寸</t>
+  </si>
+  <si>
+    <t>两个硅胶绑带，颜色在personalization里写，要新增一个提取的方法，Silicone Color后面跟的是硅胶绑带的颜色</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/1902123709/</t>
+  </si>
+  <si>
+    <t>镂空爪子骨头形狗牌</t>
+  </si>
+  <si>
+    <t>狗牌</t>
+  </si>
+  <si>
+    <t>Hollow Paw &amp; Bone Shaped Dog Tag</t>
+  </si>
+  <si>
+    <t>Personalized Paw Print Dog Tag: Stainless Steel Pet ID, Bone Shape</t>
+  </si>
+  <si>
+    <t>Engraving Option</t>
+  </si>
+  <si>
+    <t>Front Only 、Front &amp; Back</t>
+  </si>
+  <si>
+    <t>Front Only 仅正面刻录 对应Excel表一行
+Front &amp; Back 双面刻录 对应Excel表二行</t>
+  </si>
+  <si>
+    <t>https://www.etsy.com/listing/4312251710/</t>
+  </si>
+  <si>
+    <t>Custom Pet Portrait Dog Tag: Stainless Steel Bone Tag with Paw</t>
   </si>
 </sst>
 </file>
@@ -3808,7 +4087,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3827,6 +4106,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3842,44 +4124,65 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="6" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3890,7 +4193,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4425,136 +4728,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" ht="188" spans="1:1">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="159" spans="1:1">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="33" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" ht="144" spans="1:1">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="33" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" ht="173" spans="1:1">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="33" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="173" spans="1:1">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="33" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" ht="173" spans="1:1">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="33" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" ht="173" spans="1:1">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="33" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" ht="144" spans="1:1">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="33" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" ht="173" spans="1:1">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="33" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" ht="144" spans="1:1">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="33" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" ht="130" spans="1:1">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="33" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" ht="173" spans="1:1">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="33" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" ht="188" spans="1:1">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="33" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" ht="159" spans="1:1">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="33" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" ht="188" spans="1:1">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="33" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" ht="173" spans="1:1">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="34" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" ht="188" spans="1:1">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="30" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="23"/>
+      <c r="A19" s="35"/>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="23"/>
+      <c r="A20" s="35"/>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="23"/>
+      <c r="A21" s="35"/>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="23"/>
+      <c r="A22" s="35"/>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="23"/>
+      <c r="A23" s="35"/>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="23"/>
+      <c r="A24" s="35"/>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="23"/>
+      <c r="A25" s="35"/>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="23"/>
+      <c r="A26" s="35"/>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="23"/>
+      <c r="A27" s="35"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="23"/>
+      <c r="A28" s="35"/>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="23"/>
+      <c r="A29" s="35"/>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="23"/>
+      <c r="A30" s="35"/>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="23"/>
+      <c r="A31" s="35"/>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="23"/>
+      <c r="A32" s="35"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4565,1827 +4868,2518 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N48"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <dimension ref="A1:O55"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="51" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="44.3653846153846" customWidth="1"/>
-    <col min="2" max="2" width="8.80769230769231" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="9.61538461538461" customWidth="1"/>
-    <col min="4" max="4" width="13.2980769230769" customWidth="1"/>
-    <col min="5" max="5" width="74.9903846153846" style="5" customWidth="1"/>
-    <col min="6" max="6" width="25.8076923076923" customWidth="1"/>
+    <col min="4" max="4" width="23.7115384615385" customWidth="1"/>
+    <col min="5" max="5" width="38.8557692307692" style="5" customWidth="1"/>
+    <col min="6" max="6" width="13.0192307692308" customWidth="1"/>
     <col min="7" max="7" width="29.6442307692308" customWidth="1"/>
     <col min="8" max="8" width="50.6923076923077" customWidth="1"/>
     <col min="9" max="9" width="21.4326923076923" customWidth="1"/>
-    <col min="10" max="11" width="50.6923076923077" customWidth="1"/>
+    <col min="10" max="10" width="24.0384615384615" customWidth="1"/>
+    <col min="11" max="11" width="50.6923076923077" customWidth="1"/>
     <col min="12" max="12" width="17.7019230769231" customWidth="1"/>
-    <col min="13" max="14" width="49.3173076923077" customWidth="1"/>
+    <col min="13" max="13" width="28.0384615384615" customWidth="1"/>
+    <col min="14" max="14" width="33.6538461538462" customWidth="1"/>
+    <col min="15" max="15" width="17.4615384615385" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:14">
-      <c r="A1" s="6" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="8" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" ht="93" spans="1:14">
-      <c r="A2" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="9" t="s">
+    </row>
+    <row r="2" customHeight="1" spans="1:15">
+      <c r="A2" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="10" t="s">
+      <c r="B2" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="C2" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="E2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="F2" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="G2" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="H2" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="I2" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="J2" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="K2" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="L2" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="N2" s="10"/>
-    </row>
-    <row r="3" ht="66" spans="1:14">
-      <c r="A3" s="8" t="s">
+      <c r="M2" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="10" t="s">
+      <c r="N2" s="11"/>
+      <c r="O2" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:15">
+      <c r="A3" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="C3" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N3" s="11"/>
+      <c r="O3" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="I3" s="11" t="s">
+    </row>
+    <row r="4" customHeight="1" spans="1:15">
+      <c r="A4" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="N4" s="11"/>
+      <c r="O4" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:15">
+      <c r="A5" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="N5" s="11"/>
+      <c r="O5" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:15">
+      <c r="A6" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="N6" s="11"/>
+      <c r="O6" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A7" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="N7" s="15"/>
+      <c r="O7" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A8" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="H8" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" s="10" t="s">
+      <c r="I8" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="J8" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M8" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="N8" s="19"/>
+      <c r="O8" s="20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A9" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="J9" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N9" s="19"/>
+      <c r="O9" s="20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A10" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="I10" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="J10" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M10" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N10" s="19"/>
+      <c r="O10" s="20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A11" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="I11" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="J11" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="N3" s="10"/>
-    </row>
-    <row r="4" ht="93" spans="1:14">
-      <c r="A4" s="8" t="s">
+      <c r="K11" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="10" t="s">
+      <c r="L11" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M11" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="N11" s="19"/>
+      <c r="O11" s="20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A12" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" s="10" t="s">
+      <c r="C12" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="I12" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:15">
+      <c r="A13" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="N13" s="11"/>
+      <c r="O13" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:15">
+      <c r="A14" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="N14" s="11"/>
+      <c r="O14" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:15">
+      <c r="A15" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N15" s="11"/>
+      <c r="O15" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" s="4" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A16" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="F16" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="M4" s="10" t="s">
+      <c r="G16" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L16" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="N4" s="10"/>
-    </row>
-    <row r="5" ht="93" spans="1:14">
-      <c r="A5" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="M5" s="10" t="s">
+      <c r="M16" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="N16" s="11"/>
+      <c r="O16" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:15">
+      <c r="A17" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="L17" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="N5" s="10"/>
-    </row>
-    <row r="6" ht="93" spans="1:14">
-      <c r="A6" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="10" t="s">
+      <c r="M17" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="N17" s="11"/>
+      <c r="O17" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:15">
+      <c r="A18" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="N18" s="11"/>
+      <c r="O18" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:15">
+      <c r="A19" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="N19" s="11"/>
+      <c r="O19" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:15">
+      <c r="A20" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="N20" s="11"/>
+      <c r="O20" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:15">
+      <c r="A21" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N21" s="11"/>
+      <c r="O21" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:15">
+      <c r="A22" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N22" s="11"/>
+      <c r="O22" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:15">
+      <c r="A23" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="N23" s="11"/>
+      <c r="O23" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:15">
+      <c r="A24" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="N24" s="11"/>
+      <c r="O24" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:15">
+      <c r="A25" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G25" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N25" s="11"/>
+      <c r="O25" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:15">
+      <c r="A26" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="N26" s="11"/>
+      <c r="O26" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:15">
+      <c r="A27" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="N27" s="11"/>
+      <c r="O27" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:15">
+      <c r="A28" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="N28" s="11"/>
+      <c r="O28" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:15">
+      <c r="A29" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="N29" s="11"/>
+      <c r="O29" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:15">
+      <c r="A30" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N30" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="O30" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:15">
+      <c r="A31" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="F31" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="M6" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="N6" s="10"/>
-    </row>
-    <row r="7" s="2" customFormat="1" ht="93" spans="1:14">
-      <c r="A7" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="L7" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="M7" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="N7" s="13"/>
-    </row>
-    <row r="8" s="3" customFormat="1" ht="93" spans="1:14">
-      <c r="A8" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="I8" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="J8" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="K8" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="L8" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="M8" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="N8" s="16"/>
-    </row>
-    <row r="9" s="3" customFormat="1" ht="93" spans="1:14">
-      <c r="A9" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="J9" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="L9" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="N9" s="16"/>
-    </row>
-    <row r="10" s="3" customFormat="1" ht="93" spans="1:14">
-      <c r="A10" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="I10" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="J10" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="K10" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="L10" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="M10" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="N10" s="16"/>
-    </row>
-    <row r="11" s="3" customFormat="1" ht="66" spans="1:14">
-      <c r="A11" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="I11" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="J11" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="K11" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="L11" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="M11" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="N11" s="16"/>
-    </row>
-    <row r="12" s="3" customFormat="1" ht="27" spans="1:14">
-      <c r="A12" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="H12" s="16" t="s">
+      <c r="G31" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N31" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="O31" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:15">
+      <c r="A32" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="L32" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N32" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="O32" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:15">
+      <c r="A33" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="J33" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="L33" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N33" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="O33" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:15">
+      <c r="A34" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="L34" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M34" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N34" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="O34" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:15">
+      <c r="A35" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="L35" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N35" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="O35" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:15">
+      <c r="A36" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M36" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N36" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="O36" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:15">
+      <c r="A37" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="L37" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M37" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N37" s="11"/>
+      <c r="O37" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:15">
+      <c r="A38" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="G38" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N38" s="11"/>
+      <c r="O38" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:15">
+      <c r="A39" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M39" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N39" s="11"/>
+      <c r="O39" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:15">
+      <c r="A40" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="F40" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="I12" s="17" t="s">
+      <c r="G40" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="J12" s="16" t="s">
+      <c r="H40" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="K12" s="16" t="s">
+      <c r="I40" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="J40" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="L40" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M40" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N40" s="11"/>
+      <c r="O40" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="1:15">
+      <c r="A41" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="E41" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="L41" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M41" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N41" s="24"/>
+      <c r="O41" s="25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="1:15">
+      <c r="A42" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="E42" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H42" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I42" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="L42" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M42" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N42" s="24"/>
+      <c r="O42" s="25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="1:15">
+      <c r="A43" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="B43" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="C43" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="D43" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="E43" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="F43" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="G43" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="H43" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="I43" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="J43" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="K43" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M43" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N43" s="24"/>
+      <c r="O43" s="25" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="1:15">
+      <c r="A44" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="C44" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="D44" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="E44" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="F44" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="H44" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="I44" s="28" t="s">
+        <v>259</v>
+      </c>
+      <c r="J44" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="K44" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="L44" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N44" s="24"/>
+      <c r="O44" s="25" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="1:15">
+      <c r="A45" s="29" t="s">
+        <v>262</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="C45" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="D45" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="E45" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="F45" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="H45" s="24" t="s">
+        <v>264</v>
+      </c>
+      <c r="I45" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="J45" s="24" t="s">
+        <v>266</v>
+      </c>
+      <c r="K45" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="L45" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M45" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N45" s="24"/>
+      <c r="O45" s="25" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="1:15">
+      <c r="A46" s="29" t="s">
+        <v>268</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="C46" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="D46" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="E46" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="F46" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="H46" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="I46" s="28" t="s">
+        <v>275</v>
+      </c>
+      <c r="J46" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="K46" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N46" s="24"/>
+      <c r="O46" s="25" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="1:15">
+      <c r="A47" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="B47" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="C47" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="D47" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="E47" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="F47" s="28" t="s">
+        <v>279</v>
+      </c>
+      <c r="G47" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H47" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I47" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="J47" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="K47" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="L47" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N47" s="24"/>
+      <c r="O47" s="25" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="1:15">
+      <c r="A48" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="C48" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="D48" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="E48" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="F48" s="28" t="s">
+        <v>279</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H48" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I48" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="J48" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="K48" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="L48" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M48" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N48" s="24"/>
+      <c r="O48" s="25" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="1:15">
+      <c r="A49" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="C49" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="D49" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="E49" s="24" t="s">
+        <v>285</v>
+      </c>
+      <c r="F49" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="H49" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="I49" s="28" t="s">
+        <v>275</v>
+      </c>
+      <c r="J49" s="27" t="s">
+        <v>288</v>
+      </c>
+      <c r="K49" s="27" t="s">
+        <v>289</v>
+      </c>
+      <c r="L49" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M49" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N49" s="24"/>
+      <c r="O49" s="25" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="1:15">
+      <c r="A50" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B50" s="31" t="s">
+        <v>291</v>
+      </c>
+      <c r="C50" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="D50" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="E50" s="24" t="s">
+        <v>293</v>
+      </c>
+      <c r="F50" s="24" t="s">
+        <v>265</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="H50" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="I50" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="J50" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="K50" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="L50" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M50" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N50" s="24" t="s">
+        <v>297</v>
+      </c>
+      <c r="O50" s="25" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="1:15">
+      <c r="A51" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="B51" s="31" t="s">
+        <v>291</v>
+      </c>
+      <c r="C51" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="D51" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="E51" s="24" t="s">
+        <v>299</v>
+      </c>
+      <c r="F51" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="H51" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="I51" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="J51" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="K51" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M51" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N51" s="24" t="s">
+        <v>297</v>
+      </c>
+      <c r="O51" s="25" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="1:15">
+      <c r="A52" s="29" t="s">
+        <v>301</v>
+      </c>
+      <c r="B52" s="31" t="s">
+        <v>291</v>
+      </c>
+      <c r="C52" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="D52" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="E52" s="24" t="s">
+        <v>302</v>
+      </c>
+      <c r="F52" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-    </row>
-    <row r="13" ht="66" spans="1:14">
-      <c r="A13" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="L13" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="M13" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="N13" s="10"/>
-    </row>
-    <row r="14" ht="93" spans="1:14">
-      <c r="A14" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J14" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="L14" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="M14" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="N14" s="10"/>
-    </row>
-    <row r="15" ht="27" spans="1:14">
-      <c r="A15" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="K15" s="13" t="s">
+      <c r="G52" s="24" t="s">
+        <v>303</v>
+      </c>
+      <c r="H52" s="24" t="s">
+        <v>304</v>
+      </c>
+      <c r="I52" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="J52" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="K52" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="L52" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M52" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N52" s="24" t="s">
+        <v>297</v>
+      </c>
+      <c r="O52" s="25" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="53" ht="65" customHeight="1" spans="1:15">
+      <c r="A53" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>306</v>
+      </c>
+      <c r="C53" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="D53" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="E53" s="24" t="s">
+        <v>308</v>
+      </c>
+      <c r="F53" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="G53" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="I53" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="L15" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="N15" s="10"/>
-    </row>
-    <row r="16" s="4" customFormat="1" ht="93" spans="1:14">
-      <c r="A16" s="18" t="s">
+      <c r="J53" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="K53" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="L53" s="27"/>
+      <c r="M53" s="27"/>
+      <c r="N53" s="24" t="s">
+        <v>314</v>
+      </c>
+      <c r="O53" s="25" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="1:15">
+      <c r="A54" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="B54" s="26" t="s">
+        <v>316</v>
+      </c>
+      <c r="C54" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="D54" s="27" t="s">
+        <v>318</v>
+      </c>
+      <c r="E54" s="24" t="s">
+        <v>319</v>
+      </c>
+      <c r="F54" s="28" t="s">
+        <v>256</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="H54" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="I54" s="28" t="s">
+        <v>320</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="K54" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="L54" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="10" t="s">
+      <c r="M54" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="F16" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="K16" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="L16" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="M16" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="N16" s="10"/>
-    </row>
-    <row r="17" ht="39" customHeight="1" spans="1:14">
-      <c r="A17" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="K17" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="L17" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="M17" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="N17" s="10"/>
-    </row>
-    <row r="18" ht="132" spans="1:14">
-      <c r="A18" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="K18" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="L18" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="M18" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="N18" s="10"/>
-    </row>
-    <row r="19" ht="66" spans="1:14">
-      <c r="A19" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="K19" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="L19" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="M19" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="N19" s="10"/>
-    </row>
-    <row r="20" ht="212" spans="1:14">
-      <c r="A20" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="K20" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="L20" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="M20" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="N20" s="10"/>
-    </row>
-    <row r="21" ht="212" spans="1:14">
-      <c r="A21" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="K21" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="L21" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M21" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="N21" s="10"/>
-    </row>
-    <row r="22" ht="106" spans="1:14">
-      <c r="A22" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="K22" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="L22" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M22" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="N22" s="10"/>
-    </row>
-    <row r="23" ht="106" spans="1:14">
-      <c r="A23" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="J23" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="K23" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="L23" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="M23" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="N23" s="10"/>
-    </row>
-    <row r="24" ht="212" spans="1:14">
-      <c r="A24" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="H24" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="K24" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="L24" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="M24" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="N24" s="10"/>
-    </row>
-    <row r="25" ht="66" spans="1:14">
-      <c r="A25" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="J25" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="K25" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="L25" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M25" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="N25" s="10"/>
-    </row>
-    <row r="26" ht="39" customHeight="1" spans="1:14">
-      <c r="A26" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="H26" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="K26" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="L26" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="M26" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="N26" s="10"/>
-    </row>
-    <row r="27" ht="106" spans="1:14">
-      <c r="A27" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="L27" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="M27" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="N27" s="10"/>
-    </row>
-    <row r="28" ht="106" spans="1:14">
-      <c r="A28" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="J28" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="K28" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="L28" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="M28" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="N28" s="10"/>
-    </row>
-    <row r="29" ht="106" spans="1:14">
-      <c r="A29" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="J29" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="K29" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="L29" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="M29" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="N29" s="10"/>
-    </row>
-    <row r="30" ht="35" customHeight="1" spans="1:14">
-      <c r="A30" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="H30" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J30" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="K30" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="L30" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M30" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="N30" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="31" ht="132" spans="1:14">
-      <c r="A31" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I31" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="J31" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="K31" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="L31" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M31" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="N31" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="32" ht="53" spans="1:14">
-      <c r="A32" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="K32" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="L32" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M32" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="N32" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="33" ht="66" spans="1:14">
-      <c r="A33" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I33" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="K33" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="L33" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M33" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="N33" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="34" ht="66" spans="1:14">
-      <c r="A34" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I34" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="J34" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="K34" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="L34" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M34" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="N34" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="35" ht="132" spans="1:14">
-      <c r="A35" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I35" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="J35" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="K35" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="L35" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M35" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="N35" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="36" ht="53" spans="1:14">
-      <c r="A36" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="J36" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="K36" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="L36" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M36" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="N36" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="37" ht="27" spans="1:14">
-      <c r="A37" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="F37" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="G37" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="L37" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M37" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="N37" s="10"/>
-    </row>
-    <row r="38" ht="27" spans="1:14">
-      <c r="A38" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="F38" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="G38" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="H38" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="J38" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="K38" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="L38" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M38" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="N38" s="10"/>
-    </row>
-    <row r="39" ht="40" spans="1:14">
-      <c r="A39" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="F39" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M39" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="N39" s="10"/>
-    </row>
-    <row r="40" ht="93" spans="1:14">
-      <c r="A40" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="F40" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="H40" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I40" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="J40" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="K40" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="L40" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M40" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="N40" s="10"/>
-    </row>
-    <row r="41" ht="93" spans="1:14">
-      <c r="A41" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="E41" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="F41" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I41" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="J41" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="K41" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="L41" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M41" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="N41" s="21"/>
-    </row>
-    <row r="42" ht="93" spans="1:14">
-      <c r="A42" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="E42" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="F42" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G42" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I42" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="J42" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="K42" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="L42" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M42" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="N42" s="21"/>
-    </row>
-    <row r="43" spans="1:14">
-      <c r="A43" s="23"/>
-      <c r="B43" s="23"/>
-      <c r="C43" s="23"/>
-    </row>
-    <row r="44" spans="1:14">
-      <c r="A44" s="23"/>
-      <c r="B44" s="23"/>
-      <c r="C44" s="23"/>
-    </row>
-    <row r="45" spans="1:14">
-      <c r="A45" s="23"/>
-      <c r="B45" s="23"/>
-      <c r="C45" s="23"/>
-    </row>
-    <row r="46" spans="1:14">
-      <c r="A46" s="23"/>
-      <c r="B46" s="23"/>
-      <c r="C46" s="23"/>
-    </row>
-    <row r="47" spans="1:14">
-      <c r="A47" s="23"/>
-      <c r="B47" s="23"/>
-      <c r="C47" s="23"/>
-    </row>
-    <row r="48" spans="1:14">
-      <c r="A48" s="23"/>
-      <c r="B48" s="23"/>
-      <c r="C48" s="23"/>
+      <c r="N54" s="24"/>
+      <c r="O54" s="25" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="1:15">
+      <c r="A55" s="29" t="s">
+        <v>323</v>
+      </c>
+      <c r="B55" s="26" t="s">
+        <v>316</v>
+      </c>
+      <c r="C55" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="D55" s="27" t="s">
+        <v>318</v>
+      </c>
+      <c r="E55" s="24" t="s">
+        <v>324</v>
+      </c>
+      <c r="F55" s="28" t="s">
+        <v>256</v>
+      </c>
+      <c r="G55" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="H55" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="I55" s="28" t="s">
+        <v>320</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="L55" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M55" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N55" s="24"/>
+      <c r="O55" s="25" t="s">
+        <v>250</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N55" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://www.etsy.com/listing/4360752125/"/>
     <hyperlink ref="A3" r:id="rId2" display="https://www.etsy.com/listing/4433085919/"/>
     <hyperlink ref="A4" r:id="rId3" display="https://www.etsy.com/listing/1824161924/"/>
-    <hyperlink ref="A5" r:id="rId4" display="https://www.etsy.com/listing/1832405994/"/>
+    <hyperlink ref="A5" r:id="rId4" display="https://www.etsy.com/listing/1832405994/" tooltip="https://www.etsy.com/listing/1832405994/"/>
     <hyperlink ref="A6" r:id="rId5" display="https://www.etsy.com/listing/4409573815/"/>
     <hyperlink ref="A8" r:id="rId6" display="https://www.etsy.com/listing/4412172556/"/>
     <hyperlink ref="A7" r:id="rId7" display="https://www.etsy.com/listing/1845101050/"/>
@@ -6423,6 +7417,19 @@
     <hyperlink ref="A38" r:id="rId39" display="https://www.etsy.com/listing/4425999302/"/>
     <hyperlink ref="A41" r:id="rId40" display="https://www.etsy.com/listing/4443611925/"/>
     <hyperlink ref="A42" r:id="rId41" display="https://www.etsy.com/listing/4444709287/"/>
+    <hyperlink ref="A50" r:id="rId42" display="https://www.etsy.com/listing/1885600332/"/>
+    <hyperlink ref="A43" r:id="rId43" display="https://www.etsy.com/listing/1901353137/"/>
+    <hyperlink ref="A47" r:id="rId44" display="https://www.etsy.com/listing/4364446574/"/>
+    <hyperlink ref="A53" r:id="rId45" display="https://www.etsy.com/listing/4414762018/"/>
+    <hyperlink ref="A44" r:id="rId46" display="https://www.etsy.com/listing/4305925788/"/>
+    <hyperlink ref="A51" r:id="rId47" display="https://www.etsy.com/listing/4304958954/"/>
+    <hyperlink ref="A46" r:id="rId48" display="https://www.etsy.com/listing/4348238573/"/>
+    <hyperlink ref="A48" r:id="rId49" display="https://www.etsy.com/listing/4359486042/"/>
+    <hyperlink ref="A54" r:id="rId50" display="https://www.etsy.com/listing/1902123709/"/>
+    <hyperlink ref="A49" r:id="rId51" display="https://www.etsy.com/listing/4364459472/"/>
+    <hyperlink ref="A52" r:id="rId52" display="https://www.etsy.com/listing/1883818048/"/>
+    <hyperlink ref="A45" r:id="rId53" display="https://www.etsy.com/listing/4359765701/"/>
+    <hyperlink ref="A55" r:id="rId54" display="https://www.etsy.com/listing/4312251710/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/动态属性部分样例.xlsx
+++ b/动态属性部分样例.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="12560" activeTab="1"/>
+    <workbookView windowWidth="14420" windowHeight="12320" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
